--- a/Results_experiment/exp_5/preds_1111144422222222.xlsx
+++ b/Results_experiment/exp_5/preds_1111144422222222.xlsx
@@ -924,7 +924,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D2">
-        <v>3.775330066680908</v>
+        <v>4.116409301757812</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -938,7 +938,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D3">
-        <v>2.525904178619385</v>
+        <v>2.744069576263428</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -952,7 +952,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D4">
-        <v>1.424116253852844</v>
+        <v>1.389705181121826</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -966,7 +966,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D5">
-        <v>1.007929086685181</v>
+        <v>1.430898427963257</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -980,7 +980,7 @@
         <v>0.5</v>
       </c>
       <c r="D6">
-        <v>1.347401022911072</v>
+        <v>1.285759449005127</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -994,7 +994,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D7">
-        <v>3.117062330245972</v>
+        <v>2.932775974273682</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1008,7 +1008,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D8">
-        <v>0.6401963829994202</v>
+        <v>0.8986136317253113</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1022,7 +1022,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D9">
-        <v>3.593255758285522</v>
+        <v>4.256400585174561</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1036,7 +1036,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D10">
-        <v>0.6497839689254761</v>
+        <v>0.8715958595275879</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1050,7 +1050,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D11">
-        <v>1.104231953620911</v>
+        <v>1.708019495010376</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1064,7 +1064,7 @@
         <v>1.5</v>
       </c>
       <c r="D12">
-        <v>3.494739294052124</v>
+        <v>5.15567684173584</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1078,7 +1078,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D13">
-        <v>0.8901089429855347</v>
+        <v>2.09515643119812</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1092,7 +1092,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D14">
-        <v>2.297213077545166</v>
+        <v>2.303864717483521</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1106,7 +1106,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D15">
-        <v>1.380229473114014</v>
+        <v>1.916552543640137</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1120,7 +1120,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D16">
-        <v>1.160671710968018</v>
+        <v>1.701929807662964</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1134,7 +1134,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D17">
-        <v>4.00529956817627</v>
+        <v>4.086459159851074</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1148,7 +1148,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D18">
-        <v>4.024119853973389</v>
+        <v>5.767940521240234</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1162,7 +1162,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D19">
-        <v>1.043437719345093</v>
+        <v>1.669493675231934</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1176,7 +1176,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D20">
-        <v>0.9506533145904541</v>
+        <v>1.242772102355957</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1190,7 +1190,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D21">
-        <v>7.674781322479248</v>
+        <v>6.655240058898926</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1204,7 +1204,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D22">
-        <v>3.157292127609253</v>
+        <v>2.398186206817627</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1218,7 +1218,7 @@
         <v>0.5</v>
       </c>
       <c r="D23">
-        <v>2.789242744445801</v>
+        <v>3.507091760635376</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1232,7 +1232,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D24">
-        <v>0.9570443630218506</v>
+        <v>2.556347608566284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1246,7 +1246,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D25">
-        <v>2.274356126785278</v>
+        <v>3.078547716140747</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1260,7 +1260,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D26">
-        <v>1.168744206428528</v>
+        <v>2.268790721893311</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1274,7 +1274,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D27">
-        <v>0.6833096146583557</v>
+        <v>1.073977708816528</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1288,7 +1288,7 @@
         <v>4</v>
       </c>
       <c r="D28">
-        <v>2.508833885192871</v>
+        <v>2.631620645523071</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1302,7 +1302,7 @@
         <v>5.5</v>
       </c>
       <c r="D29">
-        <v>3.358280897140503</v>
+        <v>3.383702516555786</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1316,7 +1316,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D30">
-        <v>0.6705738306045532</v>
+        <v>0.9572248458862305</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1330,7 +1330,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D31">
-        <v>3.776649475097656</v>
+        <v>3.837686538696289</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1344,7 +1344,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D32">
-        <v>1.070000410079956</v>
+        <v>1.383318185806274</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1358,7 +1358,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D33">
-        <v>0.6221784353256226</v>
+        <v>0.8882392048835754</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1372,7 +1372,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D34">
-        <v>2.85870623588562</v>
+        <v>3.214585304260254</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1386,7 +1386,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D35">
-        <v>3.789842367172241</v>
+        <v>3.672615528106689</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1400,7 +1400,7 @@
         <v>7.5</v>
       </c>
       <c r="D36">
-        <v>4.143269538879395</v>
+        <v>4.746260166168213</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1414,7 +1414,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D37">
-        <v>2.559042692184448</v>
+        <v>2.385502338409424</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>3.04623007774353</v>
+        <v>4.108081817626953</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1442,7 +1442,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D39">
-        <v>2.139343500137329</v>
+        <v>2.562319040298462</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1456,7 +1456,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D40">
-        <v>0.9568498134613037</v>
+        <v>1.382720947265625</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1470,7 +1470,7 @@
         <v>11.60000038146973</v>
       </c>
       <c r="D41">
-        <v>1.492756724357605</v>
+        <v>2.849112749099731</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1484,7 +1484,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D42">
-        <v>1.958050131797791</v>
+        <v>1.839605569839478</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1498,7 +1498,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D43">
-        <v>2.831864833831787</v>
+        <v>3.544411420822144</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1512,7 +1512,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D44">
-        <v>4.237374305725098</v>
+        <v>6.224596977233887</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1526,7 +1526,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D45">
-        <v>1.122738599777222</v>
+        <v>1.926689147949219</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1540,7 +1540,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D46">
-        <v>1.669285893440247</v>
+        <v>2.493213415145874</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1554,7 +1554,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D47">
-        <v>4.932915210723877</v>
+        <v>4.961291790008545</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1568,7 +1568,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D48">
-        <v>1.040350317955017</v>
+        <v>1.504700541496277</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1582,7 +1582,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D49">
-        <v>1.123366832733154</v>
+        <v>1.592142343521118</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1596,7 +1596,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D50">
-        <v>3.5744788646698</v>
+        <v>3.956401348114014</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D51">
-        <v>3.091952085494995</v>
+        <v>3.231147050857544</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>23.29999923706055</v>
       </c>
       <c r="D52">
-        <v>17.42974090576172</v>
+        <v>17.20609855651855</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1638,7 +1638,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D53">
-        <v>0.8420091867446899</v>
+        <v>1.522672891616821</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D54">
-        <v>4.147262573242188</v>
+        <v>9.546025276184082</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1666,7 +1666,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D55">
-        <v>2.487727403640747</v>
+        <v>2.833166599273682</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D56">
-        <v>1.240842342376709</v>
+        <v>1.79030704498291</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1694,7 +1694,7 @@
         <v>2.5</v>
       </c>
       <c r="D57">
-        <v>1.008541703224182</v>
+        <v>1.873225212097168</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D58">
-        <v>4.079345703125</v>
+        <v>5.274969100952148</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D59">
-        <v>3.814120054244995</v>
+        <v>4.069699287414551</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1736,7 +1736,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D60">
-        <v>0.8432146310806274</v>
+        <v>1.842159032821655</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D61">
-        <v>1.419618248939514</v>
+        <v>1.085043668746948</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D62">
-        <v>2.647643327713013</v>
+        <v>1.782196283340454</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1778,7 +1778,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D63">
-        <v>3.351457834243774</v>
+        <v>4.005173206329346</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1792,7 +1792,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D64">
-        <v>0.9305906295776367</v>
+        <v>1.056971311569214</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1806,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>0.8781586885452271</v>
+        <v>1.260490417480469</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1820,7 +1820,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D66">
-        <v>1.914502024650574</v>
+        <v>3.011212348937988</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D67">
-        <v>3.845726490020752</v>
+        <v>2.322812795639038</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D68">
-        <v>0.6555712819099426</v>
+        <v>0.9314836859703064</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D69">
-        <v>6.398573875427246</v>
+        <v>8.291627883911133</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>2.283178806304932</v>
+        <v>2.783705234527588</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D71">
-        <v>2.351229429244995</v>
+        <v>2.558952808380127</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1904,7 +1904,7 @@
         <v>2</v>
       </c>
       <c r="D72">
-        <v>1.033787965774536</v>
+        <v>1.11516809463501</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1918,7 +1918,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D73">
-        <v>1.088068962097168</v>
+        <v>1.977766036987305</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D74">
-        <v>0.7000101804733276</v>
+        <v>0.9262367486953735</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D75">
-        <v>3.149958848953247</v>
+        <v>3.190467596054077</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1960,7 +1960,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D76">
-        <v>4.056812763214111</v>
+        <v>4.073100090026855</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1974,7 +1974,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D77">
-        <v>0.6718145608901978</v>
+        <v>1.049725770950317</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D78">
-        <v>3.210420370101929</v>
+        <v>2.022270917892456</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D79">
-        <v>0.7323720455169678</v>
+        <v>0.8706310987472534</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D80">
-        <v>0.6266359686851501</v>
+        <v>0.8788185119628906</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D81">
-        <v>1.0736004114151</v>
+        <v>1.292565107345581</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D82">
-        <v>0.6305770874023438</v>
+        <v>0.8714126944541931</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D83">
-        <v>0.6445286273956299</v>
+        <v>0.8831149935722351</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>6</v>
       </c>
       <c r="D84">
-        <v>5.669919967651367</v>
+        <v>6.789459228515625</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>0.5</v>
       </c>
       <c r="D85">
-        <v>1.014824151992798</v>
+        <v>1.289987564086914</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D86">
-        <v>0.9671612977981567</v>
+        <v>1.390703439712524</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D87">
-        <v>2.390377759933472</v>
+        <v>3.336275577545166</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D88">
-        <v>1.694642663002014</v>
+        <v>1.722684144973755</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D89">
-        <v>3.129276514053345</v>
+        <v>3.290908813476562</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D90">
-        <v>3.808093309402466</v>
+        <v>3.990705490112305</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D91">
-        <v>5.503490447998047</v>
+        <v>5.403938770294189</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D92">
-        <v>1.183136463165283</v>
+        <v>1.54949164390564</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D93">
-        <v>1.134848475456238</v>
+        <v>1.22697114944458</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D94">
-        <v>1.762304186820984</v>
+        <v>1.880335092544556</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D95">
-        <v>0.68985515832901</v>
+        <v>0.887580931186676</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D96">
-        <v>0.9980716705322266</v>
+        <v>1.153809905052185</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D97">
-        <v>3.623381614685059</v>
+        <v>3.904519557952881</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D98">
-        <v>5.779303550720215</v>
+        <v>6.275812149047852</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D99">
-        <v>8.251700401306152</v>
+        <v>8.899178504943848</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D100">
-        <v>2.865712404251099</v>
+        <v>3.014991998672485</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D101">
-        <v>4.378026008605957</v>
+        <v>4.884611129760742</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D102">
-        <v>0.8028123378753662</v>
+        <v>0.9124765396118164</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D103">
-        <v>2.410133361816406</v>
+        <v>2.800603151321411</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D104">
-        <v>3.87366509437561</v>
+        <v>4.224112987518311</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D105">
-        <v>1.812027335166931</v>
+        <v>2.347354650497437</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D106">
-        <v>1.171996593475342</v>
+        <v>1.424145221710205</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D107">
-        <v>6.551391124725342</v>
+        <v>7.268118858337402</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D108">
-        <v>0.6385977864265442</v>
+        <v>0.9338632822036743</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D109">
-        <v>3.320271730422974</v>
+        <v>2.489861011505127</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D110">
-        <v>3.159155607223511</v>
+        <v>1.858312368392944</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D111">
-        <v>3.981484174728394</v>
+        <v>4.533684730529785</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D112">
-        <v>1.074504613876343</v>
+        <v>1.175909757614136</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D113">
-        <v>2.330842971801758</v>
+        <v>2.471085071563721</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D114">
-        <v>5.009564399719238</v>
+        <v>5.441905975341797</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D115">
-        <v>2.578600883483887</v>
+        <v>3.206362724304199</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>2</v>
       </c>
       <c r="D116">
-        <v>0.9162978529930115</v>
+        <v>1.925886869430542</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D117">
-        <v>2.257857322692871</v>
+        <v>2.300364017486572</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D118">
-        <v>2.505767345428467</v>
+        <v>4.028209686279297</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>5.5</v>
       </c>
       <c r="D119">
-        <v>3.433820247650146</v>
+        <v>3.676618099212646</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D120">
-        <v>1.293025135993958</v>
+        <v>1.828191041946411</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D121">
-        <v>1.578219056129456</v>
+        <v>2.576305150985718</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D122">
-        <v>3.257775068283081</v>
+        <v>2.301441431045532</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D123">
-        <v>2.494788885116577</v>
+        <v>1.47268009185791</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>6</v>
       </c>
       <c r="D124">
-        <v>3.153124570846558</v>
+        <v>3.942490577697754</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D125">
-        <v>1.036981821060181</v>
+        <v>1.731540679931641</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>3.5</v>
       </c>
       <c r="D126">
-        <v>0.6793531179428101</v>
+        <v>1.003387212753296</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D127">
-        <v>8.655791282653809</v>
+        <v>8.509308815002441</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D128">
-        <v>0.729857325553894</v>
+        <v>1.019503593444824</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D129">
-        <v>3.108300685882568</v>
+        <v>3.422274827957153</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D130">
-        <v>1.060393214225769</v>
+        <v>1.271066308021545</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D131">
-        <v>0.862374484539032</v>
+        <v>0.9641919136047363</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="D132">
-        <v>2.082298040390015</v>
+        <v>1.626818656921387</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D133">
-        <v>1.13558304309845</v>
+        <v>1.45997142791748</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D134">
-        <v>0.9149976968765259</v>
+        <v>1.698828220367432</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>2.5</v>
       </c>
       <c r="D135">
-        <v>1.129166722297668</v>
+        <v>1.852154731750488</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D136">
-        <v>4.457815170288086</v>
+        <v>4.964333534240723</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D137">
-        <v>0.8726977109909058</v>
+        <v>1.604382038116455</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D138">
-        <v>2.674986600875854</v>
+        <v>2.865703582763672</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D139">
-        <v>2.601207733154297</v>
+        <v>2.72297739982605</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D140">
-        <v>3.349669456481934</v>
+        <v>4.672835350036621</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>14.5</v>
       </c>
       <c r="D141">
-        <v>3.911827802658081</v>
+        <v>4.072364807128906</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D142">
-        <v>1.699306011199951</v>
+        <v>1.204764485359192</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D143">
-        <v>1.512130618095398</v>
+        <v>1.642988204956055</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D144">
-        <v>1.594062685966492</v>
+        <v>1.763964414596558</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D145">
-        <v>0.9760811328887939</v>
+        <v>1.160224199295044</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>12</v>
       </c>
       <c r="D146">
-        <v>8.084541320800781</v>
+        <v>8.583443641662598</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>12.5</v>
       </c>
       <c r="D147">
-        <v>7.514659404754639</v>
+        <v>8.280399322509766</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2968,7 +2968,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D148">
-        <v>0.6413089036941528</v>
+        <v>0.8990675210952759</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>0.658507227897644</v>
+        <v>0.9502707719802856</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2996,7 +2996,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D150">
-        <v>0.9482791423797607</v>
+        <v>1.429404616355896</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3010,7 +3010,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D151">
-        <v>0.8083537220954895</v>
+        <v>0.9208208918571472</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>1.5</v>
       </c>
       <c r="D152">
-        <v>0.7883868217468262</v>
+        <v>0.8783475160598755</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3038,7 +3038,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D153">
-        <v>1.133282661437988</v>
+        <v>1.088781952857971</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3052,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="D154">
-        <v>2.616507291793823</v>
+        <v>2.106998205184937</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D155">
-        <v>4.32855224609375</v>
+        <v>5.386381149291992</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D156">
-        <v>1.547405958175659</v>
+        <v>2.121703386306763</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D157">
-        <v>0.8969976902008057</v>
+        <v>1.078377962112427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3108,7 +3108,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D158">
-        <v>1.600659132003784</v>
+        <v>2.842839002609253</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3122,7 +3122,7 @@
         <v>9.5</v>
       </c>
       <c r="D159">
-        <v>4.784060478210449</v>
+        <v>5.319747924804688</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3136,7 +3136,7 @@
         <v>5.5</v>
       </c>
       <c r="D160">
-        <v>3.418409109115601</v>
+        <v>4.977399826049805</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D161">
-        <v>1.020015835762024</v>
+        <v>1.527712345123291</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3164,7 +3164,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D162">
-        <v>2.376011371612549</v>
+        <v>1.872673034667969</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3178,7 +3178,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D163">
-        <v>0.9082877635955811</v>
+        <v>1.289902448654175</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3192,7 +3192,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D164">
-        <v>0.8326332569122314</v>
+        <v>1.030305027961731</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3206,7 +3206,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D165">
-        <v>1.380571484565735</v>
+        <v>1.110530853271484</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3220,7 +3220,7 @@
         <v>3</v>
       </c>
       <c r="D166">
-        <v>3.219172239303589</v>
+        <v>3.286395311355591</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D167">
-        <v>4.239595890045166</v>
+        <v>5.153925895690918</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D168">
-        <v>2.398967266082764</v>
+        <v>2.885773420333862</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3262,7 +3262,7 @@
         <v>2</v>
       </c>
       <c r="D169">
-        <v>1.157238602638245</v>
+        <v>1.781336545944214</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3276,7 +3276,7 @@
         <v>5</v>
       </c>
       <c r="D170">
-        <v>1.44718062877655</v>
+        <v>2.186736583709717</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D171">
-        <v>1.15932559967041</v>
+        <v>1.310195922851562</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3304,7 +3304,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D172">
-        <v>3.877472400665283</v>
+        <v>4.485482692718506</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3318,7 +3318,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D173">
-        <v>1.103413105010986</v>
+        <v>1.107491970062256</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D174">
-        <v>1.656295418739319</v>
+        <v>2.81756329536438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3346,7 +3346,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D175">
-        <v>0.9871847629547119</v>
+        <v>1.202759027481079</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>1.5</v>
       </c>
       <c r="D176">
-        <v>0.7475488185882568</v>
+        <v>0.9720484018325806</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3374,7 +3374,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D177">
-        <v>1.044220447540283</v>
+        <v>1.411343097686768</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3388,7 +3388,7 @@
         <v>3.5</v>
       </c>
       <c r="D178">
-        <v>1.004346489906311</v>
+        <v>1.387012004852295</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D179">
-        <v>1.168749570846558</v>
+        <v>1.413368225097656</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3416,7 +3416,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D180">
-        <v>0.7616363763809204</v>
+        <v>1.279388427734375</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3430,7 +3430,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D181">
-        <v>0.8210112452507019</v>
+        <v>1.093010187149048</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3444,7 +3444,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D182">
-        <v>4.374117851257324</v>
+        <v>3.458292484283447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3458,7 +3458,7 @@
         <v>1.5</v>
       </c>
       <c r="D183">
-        <v>1.900121450424194</v>
+        <v>1.308099269866943</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3472,7 +3472,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D184">
-        <v>5.180530548095703</v>
+        <v>7.019895553588867</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3486,7 +3486,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D185">
-        <v>0.6755133867263794</v>
+        <v>0.9057941436767578</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3500,7 +3500,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D186">
-        <v>2.237731695175171</v>
+        <v>1.419632911682129</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3514,7 +3514,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D187">
-        <v>0.9220926761627197</v>
+        <v>1.087941527366638</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3528,7 +3528,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D188">
-        <v>2.87024998664856</v>
+        <v>2.835413932800293</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3542,7 +3542,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D189">
-        <v>3.269094944000244</v>
+        <v>3.498990774154663</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D190">
-        <v>1.079588890075684</v>
+        <v>1.804244995117188</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3570,7 +3570,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D191">
-        <v>1.963214755058289</v>
+        <v>1.953192710876465</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3584,7 +3584,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D192">
-        <v>5.2353196144104</v>
+        <v>5.440639972686768</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3598,7 +3598,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D193">
-        <v>3.242079973220825</v>
+        <v>3.249055147171021</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3612,7 +3612,7 @@
         <v>2.5</v>
       </c>
       <c r="D194">
-        <v>1.127687215805054</v>
+        <v>1.316596150398254</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3626,7 +3626,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D195">
-        <v>1.198009729385376</v>
+        <v>1.332366228103638</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3640,7 +3640,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D196">
-        <v>1.167085289955139</v>
+        <v>2.567385673522949</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3654,7 +3654,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D197">
-        <v>3.123883247375488</v>
+        <v>3.233827829360962</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3668,7 +3668,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D198">
-        <v>1.937601685523987</v>
+        <v>2.400237083435059</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3682,7 +3682,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D199">
-        <v>4.291989803314209</v>
+        <v>3.379281282424927</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3696,7 +3696,7 @@
         <v>2.5</v>
       </c>
       <c r="D200">
-        <v>1.861275553703308</v>
+        <v>2.270066738128662</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>2.5</v>
       </c>
       <c r="D201">
-        <v>3.813557147979736</v>
+        <v>4.065596580505371</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3724,7 +3724,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D202">
-        <v>1.125818610191345</v>
+        <v>3.431960821151733</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D203">
-        <v>1.019527196884155</v>
+        <v>1.147020578384399</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3752,7 +3752,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D204">
-        <v>0.669374942779541</v>
+        <v>1.027452230453491</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3766,7 +3766,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D205">
-        <v>0.6943087577819824</v>
+        <v>1.038367509841919</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3780,7 +3780,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D206">
-        <v>4.241560459136963</v>
+        <v>4.665770053863525</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3794,7 +3794,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D207">
-        <v>1.247626423835754</v>
+        <v>3.785964727401733</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3808,7 +3808,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D208">
-        <v>1.464109182357788</v>
+        <v>2.121763467788696</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D209">
-        <v>7.612960338592529</v>
+        <v>7.05615758895874</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D210">
-        <v>1.039804577827454</v>
+        <v>2.488355875015259</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3850,7 +3850,7 @@
         <v>1.5</v>
       </c>
       <c r="D211">
-        <v>4.385059356689453</v>
+        <v>5.221631050109863</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D212">
-        <v>0.6151273250579834</v>
+        <v>0.9923902750015259</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3878,7 +3878,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D213">
-        <v>3.315373182296753</v>
+        <v>3.191596508026123</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3892,7 +3892,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D214">
-        <v>1.005489230155945</v>
+        <v>1.353521585464478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3906,7 +3906,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D215">
-        <v>1.422957539558411</v>
+        <v>1.274166464805603</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3920,7 +3920,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D216">
-        <v>0.6533178687095642</v>
+        <v>0.9073196649551392</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3934,7 +3934,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D217">
-        <v>3.052305936813354</v>
+        <v>2.109553098678589</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3948,7 +3948,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D218">
-        <v>0.9443638324737549</v>
+        <v>2.106943130493164</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>2.5</v>
       </c>
       <c r="D219">
-        <v>2.808180570602417</v>
+        <v>3.128753900527954</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3976,7 +3976,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D220">
-        <v>2.020467519760132</v>
+        <v>1.722807645797729</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3990,7 +3990,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D221">
-        <v>0.9352340698242188</v>
+        <v>1.188429355621338</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4004,7 +4004,7 @@
         <v>3.5</v>
       </c>
       <c r="D222">
-        <v>8.128045082092285</v>
+        <v>4.991084098815918</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4018,7 +4018,7 @@
         <v>6</v>
       </c>
       <c r="D223">
-        <v>3.462610483169556</v>
+        <v>3.071090459823608</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4032,7 +4032,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D224">
-        <v>7.312264442443848</v>
+        <v>6.421318054199219</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4046,7 +4046,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D225">
-        <v>3.445108890533447</v>
+        <v>3.612823247909546</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4060,7 +4060,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D226">
-        <v>1.723293662071228</v>
+        <v>1.678797006607056</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4074,7 +4074,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D227">
-        <v>3.410599946975708</v>
+        <v>3.461589097976685</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4088,7 +4088,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D228">
-        <v>3.077073335647583</v>
+        <v>4.153190612792969</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4102,7 +4102,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D229">
-        <v>3.421023845672607</v>
+        <v>4.404306888580322</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4116,7 +4116,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D230">
-        <v>4.968554496765137</v>
+        <v>4.95043420791626</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4130,7 +4130,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D231">
-        <v>3.885605335235596</v>
+        <v>4.13383960723877</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4144,7 +4144,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D232">
-        <v>1.18612813949585</v>
+        <v>1.560681104660034</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4158,7 +4158,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D233">
-        <v>2.239119529724121</v>
+        <v>1.449338436126709</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="D234">
-        <v>3.767663955688477</v>
+        <v>5.646868705749512</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4186,7 +4186,7 @@
         <v>4</v>
       </c>
       <c r="D235">
-        <v>1.834639191627502</v>
+        <v>2.457659244537354</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4200,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="D236">
-        <v>0.9442183971405029</v>
+        <v>1.583395719528198</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4214,7 +4214,7 @@
         <v>8</v>
       </c>
       <c r="D237">
-        <v>1.446879863739014</v>
+        <v>2.701575517654419</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4228,7 +4228,7 @@
         <v>10</v>
       </c>
       <c r="D238">
-        <v>8.400985717773438</v>
+        <v>8.875768661499023</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4242,7 +4242,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D239">
-        <v>6.895836353302002</v>
+        <v>7.562203884124756</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4256,7 +4256,7 @@
         <v>19</v>
       </c>
       <c r="D240">
-        <v>12.92714023590088</v>
+        <v>13.2929859161377</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4270,7 +4270,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D241">
-        <v>0.6564934253692627</v>
+        <v>1.085037708282471</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4284,7 +4284,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D242">
-        <v>1.336680293083191</v>
+        <v>1.437884330749512</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4298,7 +4298,7 @@
         <v>3</v>
       </c>
       <c r="D243">
-        <v>1.165290355682373</v>
+        <v>1.831578254699707</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4312,7 +4312,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D244">
-        <v>2.071418046951294</v>
+        <v>3.71373724937439</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4326,7 +4326,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D245">
-        <v>1.590150713920593</v>
+        <v>1.863333702087402</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4340,7 +4340,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D246">
-        <v>1.37183678150177</v>
+        <v>1.948415279388428</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4354,7 +4354,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D247">
-        <v>6.135746955871582</v>
+        <v>8.073952674865723</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4368,7 +4368,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D248">
-        <v>1.112833857536316</v>
+        <v>1.93066143989563</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>8</v>
       </c>
       <c r="D249">
-        <v>2.108000755310059</v>
+        <v>3.773023843765259</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4396,7 +4396,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D250">
-        <v>8.313889503479004</v>
+        <v>8.784380912780762</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4410,7 +4410,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D251">
-        <v>3.30936598777771</v>
+        <v>4.819026947021484</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4424,7 +4424,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>4.094668388366699</v>
+        <v>4.140039443969727</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4438,7 +4438,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D253">
-        <v>5.707266807556152</v>
+        <v>5.417840957641602</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4452,7 +4452,7 @@
         <v>0.5</v>
       </c>
       <c r="D254">
-        <v>1.101228952407837</v>
+        <v>1.601955652236938</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4466,7 +4466,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D255">
-        <v>0.6981698870658875</v>
+        <v>0.8861830234527588</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4480,7 +4480,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D256">
-        <v>4.271461486816406</v>
+        <v>4.815854072570801</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4494,7 +4494,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D257">
-        <v>1.395364999771118</v>
+        <v>2.43572998046875</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D258">
-        <v>3.467824935913086</v>
+        <v>2.789103746414185</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4522,7 +4522,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D259">
-        <v>0.979118287563324</v>
+        <v>1.145561218261719</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4536,7 +4536,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D260">
-        <v>0.9691439867019653</v>
+        <v>1.113398313522339</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4550,7 +4550,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D261">
-        <v>0.6698906421661377</v>
+        <v>0.9337097406387329</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4564,7 +4564,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D262">
-        <v>0.9513052701950073</v>
+        <v>1.461815357208252</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D263">
-        <v>3.556868553161621</v>
+        <v>4.24722146987915</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D264">
-        <v>0.6797542572021484</v>
+        <v>0.9417064189910889</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4606,7 +4606,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D265">
-        <v>1.060045003890991</v>
+        <v>1.553959846496582</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4620,7 +4620,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D266">
-        <v>5.207301139831543</v>
+        <v>6.859500885009766</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4634,7 +4634,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D267">
-        <v>0.8054461479187012</v>
+        <v>1.237550020217896</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4648,7 +4648,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D268">
-        <v>2.881000757217407</v>
+        <v>3.246469020843506</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4662,7 +4662,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D269">
-        <v>3.182959079742432</v>
+        <v>3.298663377761841</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4676,7 +4676,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D270">
-        <v>2.55162501335144</v>
+        <v>3.445783853530884</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4690,7 +4690,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D271">
-        <v>0.7068498134613037</v>
+        <v>0.9215911030769348</v>
       </c>
     </row>
   </sheetData>
